--- a/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
@@ -461,9 +461,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Summary'!$A$5:$A$16</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -489,9 +489,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Summary'!$A$5:$A$16</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -517,9 +517,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Summary'!$A$5:$A$16</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -545,9 +545,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Summary'!$A$5:$A$16</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -565,6 +565,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -583,6 +584,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>
@@ -621,9 +623,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>
@@ -790,9 +794,9 @@
             </spPr>
           </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Summary'!$A$22:$A$25</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -809,9 +813,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>
@@ -850,6 +856,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -868,6 +875,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:solidFill>

--- a/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>Hydrogen &amp; Decarbonised Gas package, RED III, IPCEIs</t>
+          <t>RED III, EED, EPBD, Net-Zero Industry Act</t>
         </is>
       </c>
       <c r="G2" s="18" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>The Ecodesign Directive has been mainly focused on energy efficiency; product circularity has been added only in recent years, and its scope remained limited to energy products.</t>
+          <t>The Ecodesign Directive has been mainly focused on energy efficiency; product circularity has been added in recent years, and its scope remained limited to energy products.</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -2357,7 +2357,11 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr"/>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>TAGGING: the report tags TWO barriers in this sentence — the failure to incentivise efficiency is an (ambition gap) and the pull towards larger, less-efficient ZEVs is a (policy inconsistency). This row carries the ambition tag; the inconsistency is recorded here rather than as a separate row. The report's phrase 'these policies' also covers the CO2 standards for HDVs, the AFIR, the revised Clean Vehicles Directive and EU State aid guidelines, not only the car and van standards.</t>
+        </is>
+      </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
           <t>Report</t>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>Implementation of the modal-shift measures (notably the Rail Freight Corridor Regulation and the Combined Transport Directive) has been incomplete and heterogeneous across Member States.</t>
+          <t>Implementation of the modal-shift measures has been incomplete and heterogeneous across Member States.</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -2573,7 +2577,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>There are well-founded suspicions of fraud in the labelling of transport biofuels as sustainable under RED III.</t>
+          <t>There are well-founded suspicions of fraud in the labelling of transport biofuels as sustainable.</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -2906,7 +2910,11 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="K23" s="21" t="inlineStr"/>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>TAGGING: the report tags TWO barriers here — the fossil-gas subsidies allowed under the ETD are a (policy inconsistency), and the insufficiently robust EU standards and resulting lock-in are a (policy gap). This row carries the inconsistency tag; the policy gap is recorded here.</t>
+        </is>
+      </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t>Report</t>
@@ -3376,7 +3384,7 @@
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>“Furthermore, the incentives for using forest biomass for energy purposes versus maximising the LULUCF carbon sink continue to be unevenly distributed in the absence of a financial incentive for land managers to reduce emissions and increase removals in the LULUCF sector (policy gap).”</t>
+          <t>“Furthermore, the incentives for using forest biomass for energy purposes versus maximising the LULUCF carbon sink continue to be unevenly distributed in the absence of a financial incentive for land managers to reduce emissions and increase removals in the LULUCF sector (policy gap) (see also Chapter 10 'Pricing emissions and rewarding removals').”</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -3516,7 +3524,11 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="K33" s="21" t="inlineStr"/>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>TAGGING: the report tags TWO barriers in this sentence — the specific exemptions are an (ambition gap) and the monitoring and compliance issues, including fraud, are an (implementation gap). This row carries the ambition tag; the implementation gap is recorded here.</t>
+        </is>
+      </c>
       <c r="L33" s="21" t="inlineStr">
         <is>
           <t>Report</t>
@@ -3676,7 +3688,7 @@
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>CAP eco-schemes, Carbon Removals Certification</t>
+          <t>CAP eco-schemes</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
@@ -3737,7 +3749,7 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>RED III, Governance Regulation reporting</t>
+          <t>RED III, LULUCF Regulation reporting</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
@@ -3882,7 +3894,11 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="K39" s="21" t="inlineStr"/>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>SOURCING: the quoted passage on p. 224 carries no inline gap tag. The 'policy gap' type comes from Table 16 on p. 227 ('Agriculture/food and land use are not covered by explicit carbon pricing').</t>
+        </is>
+      </c>
       <c r="L39" s="21" t="inlineStr">
         <is>
           <t>Report</t>
@@ -4525,7 +4541,7 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>The proposed Strategic Technologies for Europe Platform, presented as a first step towards an EU Sovereignty Fund, carries too limited a budget (EUR 10 billion, versus more than EUR 300 billion per year in State aid in 2021) to be sufficiently effective in closing the investment gap.</t>
+          <t>The proposed Strategic Technologies for Europe Platform, presented as a first step towards an EU Sovereignty Fund, carries too limited a budget (EUR 10 billion, versus more than EUR 300 billion per year in State aid in 2021) to be sufficiently effective in countering the risk that relaxed State aid rules fragment the EU single market.</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -5389,12 +5405,12 @@
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>“Deficits in transparency and in public engagement are observed in NECP preparation at the national level (implementation gap). The Committee of the Regions points out that the dialogues are often not permanent and the NECPs are not always in tune with subnational climate policies (implementation gap).”</t>
+          <t>“Deficits in transparency and in public engagement are observed in NECP preparation at the national level (implementation gap). […] The Committee of the Regions points out that the dialogues are often not permanent and the NECPs are not always in tune with subnational climate policies (implementation gap).”</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Ch. 14 Climate governance, pp. 268-269, p. 268, line 22</t>
+          <t>Ch. 14 Climate governance, pp. 268–269 (two sentences joined — see the ellipsis in the quote)</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">

--- a/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gap tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Legend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gap tracker'!$A$1:$M$67</definedName>
@@ -411,13 +411,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1100" b="0">
                 <a:solidFill>
@@ -452,10 +452,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="B04545"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -480,10 +480,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="F59E2D"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -508,10 +508,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="648ECA"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -536,10 +536,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="B487C7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -570,8 +570,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -586,7 +586,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -594,8 +594,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -629,7 +629,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -637,8 +637,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -665,8 +665,8 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="800">
               <a:solidFill>
@@ -691,7 +691,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -700,13 +700,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1100" b="0">
                 <a:solidFill>
@@ -741,17 +741,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B04545"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -760,10 +760,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F59E2D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -772,10 +772,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4D7E83"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -784,10 +784,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="6E7A7B"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -819,7 +819,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -827,8 +827,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -861,8 +861,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -877,7 +877,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -885,8 +885,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -913,7 +913,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -922,7 +922,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -937,9 +937,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -959,9 +959,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Policy-Gap-Tracker_2026-07.xlsx
@@ -438,6 +438,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -581,6 +582,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -727,6 +729,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -872,6 +875,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -949,7 +953,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4680000" cy="2700000"/>
